--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.169" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.169" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.169.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0169.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0169.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.169" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.169" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54 â€” 55</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 60</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 162</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: C</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 64</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: I</t>
+          <t>L34: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -691,7 +699,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -727,12 +739,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54â€”55</t>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +756,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: I</t>
+          <t>L36: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -790,12 +802,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 55â€”56â€”57</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -807,7 +819,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: i</t>
+          <t>L37: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -853,12 +865,12 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54 â€” 55</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -870,7 +882,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: J</t>
+          <t>L38: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -910,14 +922,10 @@
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 57â€”58</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -929,7 +937,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 54</t>
+          <t>L39: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -965,14 +973,10 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58â€”59</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -984,7 +988,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 64</t>
+          <t>L43: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1023,7 +1027,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1035,7 +1039,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 54</t>
+          <t>L45: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1057,12 +1061,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1074,7 +1078,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 54</t>
+          <t>L47: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1125,7 +1129,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 64</t>
+          <t>L49: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1159,12 +1163,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1176,19 +1180,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L33: symbol-only separator/garbage line :: 55-56-57</t>
+          <t>L30: symbol-only separator/garbage line :: 54 — 55</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L53: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1227,19 +1231,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: .</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: ]</t>
+          <t>L55: symbol-only separator/garbage line :: 54—55</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1278,19 +1282,19 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: 57-58</t>
+          <t>L33: symbol-only separator/garbage line :: 55-56-57</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 60</t>
+          <t>L57: symbol-only separator/garbage line :: 55—56—57</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1327,21 +1331,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: .</t>
+          <t>L35: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 63</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1378,21 +1378,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 107â€”108</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 60</t>
+          <t>L36: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 58</t>
+          <t>L63: isolated marker/symbol line :: ]</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1429,21 +1425,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L38: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 61</t>
+          <t>L65: symbol-only separator/garbage line :: 57—58</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1468,21 +1460,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 63</t>
+          <t>L39: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: .62</t>
+          <t>L67: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1507,21 +1495,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Question as to the Jurisdiction of the Court of Chancery 8â€”9</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 58</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 62</t>
+          <t>L69: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1551,12 +1535,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 61</t>
+          <t>L42: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 62</t>
+          <t>L71: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1586,12 +1570,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 62</t>
+          <t>L44: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L73: symbol-only separator/garbage line :: 58—59</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1621,12 +1605,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 62</t>
+          <t>L46: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1656,12 +1640,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 62</t>
+          <t>L50: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L78: symbol-only separator/garbage line :: .62</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1691,12 +1675,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 107-108</t>
+          <t>L52: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1726,12 +1710,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 8</t>
+          <t>L54: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1761,12 +1745,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 8</t>
+          <t>L56: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1796,12 +1780,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 162</t>
+          <t>L59: symbol-only separator/garbage line :: 107-108</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1831,12 +1815,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 4</t>
+          <t>L65: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 8</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1866,12 +1850,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 2</t>
+          <t>L67: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 8</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1901,12 +1885,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: C</t>
+          <t>L70: isolated marker/symbol line :: 162</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1936,12 +1920,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 1</t>
+          <t>L74: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1971,10 +1955,14 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 54</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr"/>
+          <t>L77: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr"/>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2002,10 +1990,14 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 64</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr"/>
+          <t>L80: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 107—108</t>
+        </is>
+      </c>
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr"/>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2033,10 +2025,14 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 54</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr"/>
+          <t>L82: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L138: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2064,10 +2060,14 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 54</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr"/>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L140: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2095,10 +2095,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L90: isolated marker/symbol line :: 54</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2126,10 +2130,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 64</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L92: isolated marker/symbol line :: 64</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2157,7 +2165,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: 55-56-57</t>
+          <t>L94: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2188,7 +2196,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: .</t>
+          <t>L96: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2219,7 +2227,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L110: symbol-only separator/garbage line :: 57-58</t>
+          <t>L101: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2250,7 +2258,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: .</t>
+          <t>L102: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2281,7 +2289,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 60</t>
+          <t>L104: symbol-only separator/garbage line :: 54 — 55</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2312,7 +2320,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2343,7 +2351,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 63</t>
+          <t>L107: symbol-only separator/garbage line :: 55-56-57</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2374,7 +2382,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 58</t>
+          <t>L109: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2405,7 +2413,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 61</t>
+          <t>L110: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2436,7 +2444,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 62</t>
+          <t>L112: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2467,7 +2475,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 62</t>
+          <t>L113: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2498,7 +2506,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 62</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2529,7 +2537,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L136: symbol-only separator/garbage line :: 107-108</t>
+          <t>L116: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2560,7 +2568,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 8</t>
+          <t>L119: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2591,7 +2599,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 8</t>
+          <t>L121: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2606,6 +2614,223 @@
       <c r="X52" s="1" t="inlineStr"/>
       <c r="Y52" s="1" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: 61</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L128: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
+      <c r="L55" s="1" t="inlineStr"/>
+      <c r="M55" s="1" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>L131: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr"/>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+      <c r="W55" s="1" t="inlineStr"/>
+      <c r="X55" s="1" t="inlineStr"/>
+      <c r="Y55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr"/>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
+      <c r="L56" s="1" t="inlineStr"/>
+      <c r="M56" s="1" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>L133: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr"/>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr"/>
+      <c r="S56" s="1" t="inlineStr"/>
+      <c r="T56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="inlineStr"/>
+      <c r="V56" s="1" t="inlineStr"/>
+      <c r="W56" s="1" t="inlineStr"/>
+      <c r="X56" s="1" t="inlineStr"/>
+      <c r="Y56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
+      <c r="L57" s="1" t="inlineStr"/>
+      <c r="M57" s="1" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>L136: symbol-only separator/garbage line :: 107-108</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr"/>
+      <c r="V57" s="1" t="inlineStr"/>
+      <c r="W57" s="1" t="inlineStr"/>
+      <c r="X57" s="1" t="inlineStr"/>
+      <c r="Y57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr"/>
+      <c r="B58" s="1" t="inlineStr"/>
+      <c r="C58" s="1" t="inlineStr"/>
+      <c r="D58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr"/>
+      <c r="H58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr"/>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
+      <c r="L58" s="1" t="inlineStr"/>
+      <c r="M58" s="1" t="inlineStr"/>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>L144: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr"/>
+      <c r="P58" s="1" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr"/>
+      <c r="R58" s="1" t="inlineStr"/>
+      <c r="S58" s="1" t="inlineStr"/>
+      <c r="T58" s="1" t="inlineStr"/>
+      <c r="U58" s="1" t="inlineStr"/>
+      <c r="V58" s="1" t="inlineStr"/>
+      <c r="W58" s="1" t="inlineStr"/>
+      <c r="X58" s="1" t="inlineStr"/>
+      <c r="Y58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr"/>
+      <c r="B59" s="1" t="inlineStr"/>
+      <c r="C59" s="1" t="inlineStr"/>
+      <c r="D59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr"/>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr"/>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
+      <c r="L59" s="1" t="inlineStr"/>
+      <c r="M59" s="1" t="inlineStr"/>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>L146: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr"/>
+      <c r="P59" s="1" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr"/>
+      <c r="R59" s="1" t="inlineStr"/>
+      <c r="S59" s="1" t="inlineStr"/>
+      <c r="T59" s="1" t="inlineStr"/>
+      <c r="U59" s="1" t="inlineStr"/>
+      <c r="V59" s="1" t="inlineStr"/>
+      <c r="W59" s="1" t="inlineStr"/>
+      <c r="X59" s="1" t="inlineStr"/>
+      <c r="Y59" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
